--- a/Output/00_PrettyEditedTables.xlsx
+++ b/Output/00_PrettyEditedTables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pascku\Repos\02TimeAndTiesControl\Output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC635610-C032-48E9-B64B-4FF4C4F2E7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1471A46F-D331-4467-8766-FD590B1CFB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22510" yWindow="760" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MVPA" sheetId="2" r:id="rId1"/>
@@ -1043,6 +1043,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1058,10 +1062,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1359,59 +1359,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E876E58-69A6-40D5-A138-00AF2B8A39AF}">
   <dimension ref="A2:I36"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="0.86328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.265625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="0.86328125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.265625" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.73046875" style="3"/>
+    <col min="1" max="1" width="41.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="0.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="0.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="21" customFormat="1" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" s="21" customFormat="1" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
       <c r="G2" s="20"/>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="37" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="34"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34" t="s">
+      <c r="H3" s="36"/>
+      <c r="I3" s="36" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>50</v>
       </c>
@@ -1436,450 +1436,450 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="34" t="s">
         <v>210</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="34" t="s">
         <v>194</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="34" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="16"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="16"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="34" t="s">
         <v>211</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="34" t="s">
         <v>83</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="34" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="34" t="s">
         <v>212</v>
       </c>
       <c r="D8" s="7"/>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="34" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I8" s="34" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="34" t="s">
         <v>213</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="34" t="s">
         <v>214</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="34" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="34" t="s">
         <v>215</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="34" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="7"/>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="34" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="34" t="s">
         <v>216</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="34" t="s">
         <v>217</v>
       </c>
       <c r="G11" s="7"/>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="34" t="s">
         <v>218</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="34" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="34" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="34" t="s">
         <v>219</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="34" t="s">
         <v>220</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="34" t="s">
         <v>209</v>
       </c>
       <c r="D14" s="7"/>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="34" t="s">
         <v>221</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="H14" s="39" t="s">
+      <c r="H14" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="34" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="34" t="s">
         <v>222</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="34" t="s">
         <v>223</v>
       </c>
       <c r="G15" s="7"/>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="34" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
       <c r="D17" s="16"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="16"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="34" t="s">
         <v>224</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="34" t="s">
         <v>225</v>
       </c>
       <c r="G18" s="7"/>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="34" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="34" t="s">
         <v>226</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="34" t="s">
         <v>227</v>
       </c>
       <c r="G19" s="7"/>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="34" t="s">
         <v>228</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="34" t="s">
         <v>229</v>
       </c>
       <c r="G20" s="7"/>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="34" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="34" t="s">
         <v>230</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="E21" s="39" t="s">
+      <c r="E21" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="34" t="s">
         <v>231</v>
       </c>
       <c r="G21" s="7"/>
-      <c r="H21" s="39" t="s">
+      <c r="H21" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="39" t="s">
+      <c r="I21" s="34" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="34" t="s">
         <v>232</v>
       </c>
       <c r="D22" s="7"/>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="34" t="s">
         <v>233</v>
       </c>
       <c r="G22" s="7"/>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="39" t="s">
+      <c r="I22" s="34" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="34" t="s">
         <v>234</v>
       </c>
       <c r="D23" s="7"/>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F23" s="34" t="s">
         <v>235</v>
       </c>
       <c r="G23" s="7"/>
-      <c r="H23" s="39" t="s">
+      <c r="H23" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="39" t="s">
+      <c r="I23" s="34" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
         <v>246</v>
       </c>
@@ -1889,14 +1889,14 @@
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="39" t="s">
+      <c r="I24" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -1906,45 +1906,45 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:9" s="21" customFormat="1" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" s="21" customFormat="1" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19"/>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
       <c r="G26" s="20"/>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I26" s="35" t="s">
+      <c r="I26" s="37" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="38" t="s">
         <v>1</v>
       </c>
       <c r="D27" s="9"/>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="36"/>
+      <c r="F27" s="38"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36" t="s">
+      <c r="H27" s="38"/>
+      <c r="I27" s="38" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>28</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>6</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>97</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>98</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>99</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>100</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
         <v>101</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
         <v>102</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>51</v>
       </c>
@@ -2186,30 +2186,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660B36E2-614D-4BFC-9DFD-65D5E3ED2816}">
   <dimension ref="A2:K34"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.796875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="1" style="3" customWidth="1"/>
-    <col min="5" max="5" width="7.86328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.796875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.73046875" style="3"/>
+    <col min="5" max="5" width="7.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="38"/>
+      <c r="C2" s="40"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="37"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="F2" s="39"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>50</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>96</v>
       </c>
@@ -2255,7 +2255,7 @@
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>97</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>98</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>99</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>100</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>101</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
         <v>102</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
         <v>16</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
         <v>244</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
         <v>245</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>247</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
         <v>103</v>
       </c>
@@ -2437,7 +2437,7 @@
       <c r="E16" s="32"/>
       <c r="F16" s="32"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>104</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>105</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>106</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
         <v>107</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>108</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
         <v>109</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>246</v>
       </c>
@@ -2555,26 +2555,26 @@
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="C25" s="35"/>
+      <c r="C25" s="37"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="37" t="s">
+      <c r="E25" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="37"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>28</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>6</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>97</v>
       </c>
@@ -2632,7 +2632,7 @@
       <c r="J28" s="17"/>
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>98</v>
       </c>
@@ -2652,7 +2652,7 @@
       <c r="J29" s="17"/>
       <c r="K29" s="17"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>99</v>
       </c>
@@ -2672,7 +2672,7 @@
       <c r="J30" s="17"/>
       <c r="K30" s="17"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>100</v>
       </c>
@@ -2692,7 +2692,7 @@
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>101</v>
       </c>
@@ -2712,7 +2712,7 @@
       <c r="J32" s="17"/>
       <c r="K32" s="17"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>102</v>
       </c>
@@ -2732,7 +2732,7 @@
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>51</v>
       </c>
